--- a/gst_recon/sample_data/tally_purchase_register_2025-04.xlsx
+++ b/gst_recon/sample_data/tally_purchase_register_2025-04.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,6 +526,11 @@
           <t>Input IGST 12%</t>
         </is>
       </c>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>Narration</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1617,11 +1622,11 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45762</v>
+        <v>45765</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Local Hardware (URD)</t>
+          <t>Annapurna Caterers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1634,35 +1639,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LH-55</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>12-04-2025</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>ANC/77</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45765</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>27AAJFA2468S1ZQ</t>
+        </is>
+      </c>
       <c r="H32" t="n">
-        <v>2950</v>
+        <v>9440</v>
       </c>
       <c r="I32" t="n">
-        <v>2500</v>
+        <v>8000</v>
       </c>
       <c r="K32" t="n">
-        <v>225</v>
+        <v>720</v>
       </c>
       <c r="L32" t="n">
-        <v>225</v>
+        <v>720</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Staff lunch – Diwali function</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45762</v>
+        <v>45755</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pune Packaging Co</t>
+          <t>Shree Roadways (GTA)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1675,40 +1687,129 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>SRW-310</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>27ABKPS1357T1ZO</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>21000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>500</v>
+      </c>
+      <c r="N33" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Freight inward – GTA under RCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Local Hardware (URD)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Purchase</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>29</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LH-55</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>12-04-2025</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>2950</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K34" t="n">
+        <v>225</v>
+      </c>
+      <c r="L34" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pune Packaging Co</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Purchase</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>30</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>PPK/499</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>31-04-2025</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>27AAFFP4321M1Z3</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="H35" t="n">
         <v>4720</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I35" t="n">
         <v>4000</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K35" t="n">
         <v>360</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L35" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="H34">
-        <f>SUM(H6:H33)</f>
+      <c r="H36">
+        <f>SUM(H6:H35)</f>
         <v/>
       </c>
     </row>
